--- a/education_forms/014_music_and_play_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/014_music_and_play_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz</t>
+          <t>music_and_play_knowledge_quiz_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>How often do you listen to music?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_1</t>
+          <t>music_and_play_knowledge_quiz_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_2</t>
+          <t>music_and_play_knowledge_quiz_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Which instrument are you familiar with?</t>
+          <t>Which instrument do you usually play?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_3</t>
+          <t>music_and_play_knowledge_quiz_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_4</t>
+          <t>music_and_play_knowledge_quiz_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,58 +635,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_5</t>
+          <t>music_and_play_knowledge_quiz_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Which music style do you like best?</t>
+          <t>How often do you go to concerts?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_6</t>
+          <t>music_and_play_knowledge_quiz_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How do you usually listen to music?</t>
+          <t>Which music style do you like best?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_7</t>
+          <t>music_and_play_knowledge_quiz_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your favorite music artist?</t>
+          <t>How do you usually purchase music?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_8</t>
+          <t>music_and_play_knowledge_quiz_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How often do you go to concerts?</t>
+          <t>What is your favorite music artist?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_9</t>
+          <t>music_and_play_knowledge_quiz_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your favorite music festival?</t>
+          <t>How often do you go to music festivals?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_10</t>
+          <t>music_and_play_knowledge_quiz_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_11</t>
+          <t>music_and_play_knowledge_quiz_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How do you usually purchase music?</t>
+          <t>What is your favorite music festival?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What is your favorite music genre?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Which music style do you like best?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>How often do you go to concerts?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What is your favorite music artist?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How long do you usually listen to music?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How do you usually purchase music?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How often do you go to music festivals?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is your favorite music genre?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Which music style do you like best?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How often do you go to concerts?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is your favorite music artist?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How long do you usually listen to music?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>music_and_play_knowledge_quiz_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How often do you purchase music?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -1148,658 +849,658 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_2_choices</t>
+          <t>music_and_play_knowledge_quiz_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_2_choices</t>
+          <t>music_and_play_knowledge_quiz_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_4_choices</t>
+          <t>music_and_play_knowledge_quiz_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_4_choices</t>
+          <t>music_and_play_knowledge_quiz_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_5_choices</t>
+          <t>music_and_play_knowledge_quiz_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_5_choices</t>
+          <t>music_and_play_knowledge_quiz_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_6_choices</t>
+          <t>music_and_play_knowledge_quiz_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>piano</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Piano</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_6_choices</t>
+          <t>music_and_play_knowledge_quiz_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Guitar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_7_choices</t>
+          <t>music_and_play_knowledge_quiz_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>drums</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Drums</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_7_choices</t>
+          <t>music_and_play_knowledge_quiz_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bass</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bass</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_8_choices</t>
+          <t>music_and_play_knowledge_quiz_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_8_choices</t>
+          <t>music_and_play_knowledge_quiz_5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_9_choices</t>
+          <t>music_and_play_knowledge_quiz_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_9_choices</t>
+          <t>music_and_play_knowledge_quiz_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_11_choices</t>
+          <t>music_and_play_knowledge_quiz_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_11_choices</t>
+          <t>music_and_play_knowledge_quiz_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_13_choices</t>
+          <t>music_and_play_knowledge_quiz_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_13_choices</t>
+          <t>music_and_play_knowledge_quiz_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_14_choices</t>
+          <t>music_and_play_knowledge_quiz_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_14_choices</t>
+          <t>music_and_play_knowledge_quiz_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_15_choices</t>
+          <t>music_and_play_knowledge_quiz_7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_15_choices</t>
+          <t>music_and_play_knowledge_quiz_7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_16_choices</t>
+          <t>music_and_play_knowledge_quiz_8_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_16_choices</t>
+          <t>music_and_play_knowledge_quiz_8_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>in-store</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>In-store</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_18_choices</t>
+          <t>music_and_play_knowledge_quiz_8_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>streaming</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Streaming</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_18_choices</t>
+          <t>music_and_play_knowledge_quiz_8_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>downloading</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Downloading</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_19_choices</t>
+          <t>music_and_play_knowledge_quiz_9_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>classical_artist</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Classical Artist</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_19_choices</t>
+          <t>music_and_play_knowledge_quiz_9_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pop_artist</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pop Artist</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_20_choices</t>
+          <t>music_and_play_knowledge_quiz_9_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rock_artist</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rock Artist</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_20_choices</t>
+          <t>music_and_play_knowledge_quiz_9_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>jazz_artist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Jazz Artist</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_21_choices</t>
+          <t>music_and_play_knowledge_quiz_10_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_21_choices</t>
+          <t>music_and_play_knowledge_quiz_10_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_22_choices</t>
+          <t>music_and_play_knowledge_quiz_10_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_22_choices</t>
+          <t>music_and_play_knowledge_quiz_10_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_23_choices</t>
+          <t>music_and_play_knowledge_quiz_12_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>classical_festival</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Classical Festival</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_23_choices</t>
+          <t>music_and_play_knowledge_quiz_12_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pop_festival</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pop Festival</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_25_choices</t>
+          <t>music_and_play_knowledge_quiz_12_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rock_festival</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rock Festival</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>music_and_play_knowledge_quiz_25_choices</t>
+          <t>music_and_play_knowledge_quiz_12_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>jazz_festival</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Jazz Festival</t>
         </is>
       </c>
     </row>
